--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96587</v>
+        <v>96593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96593</v>
+        <v>96597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96597</v>
+        <v>96599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96635</v>
+        <v>96637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96637</v>
+        <v>96643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96643</v>
+        <v>96655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32652-2026 artfynd.xlsx
+++ b/artfynd/A 32652-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078330</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137078332</v>
       </c>
       <c r="B3" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
